--- a/deliverables/deliverables-20260120-0030/Master_Template.xlsx
+++ b/deliverables/deliverables-20260120-0030/Master_Template.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Reference" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,10 +20,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0_);(#,##0.0)"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +57,13 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -108,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,16 +137,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -504,6 +519,425 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>═══ DEBT STRUCTURE DECISION TREE ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>Cash Flow Type</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>Key Formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>Contracted (PPA, tariff)</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Sculpted to 1.30-1.40x DSCR</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>Prin = MIN(MAX(0, CFADS/DSCR − Int), Bal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>Merchant (power, midstream)</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>75% Cash Sweep, 1.25x min</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>Sweep = MIN(Excess × 75%, Bal − Sched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Hybrid/Semi-contracted</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Sweep + tighter covenant</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>Same as sweep with 1.30x DSCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>═══ UNIT CONVERSIONS ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>Calculation</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Common Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Fuel Cost ($mm)</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Gen × HR × Gas / 1E9</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>÷1E6 → 1000× too high</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Energy Revenue ($mm)</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Gen × Price / 1E6</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>Forgetting ÷1E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>Capacity Revenue ($mm)</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>UCAP × Price × 1000 / 1E6</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>Missing ×1000 (price is $/kW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Peaker Generation (MWh)</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Capacity × Dispatch Hrs × Avail</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>Using CF × 8760 (10× too high)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>═══ DSRA LOGIC ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>DSRA Target Y(n) = Scheduled DS Y(n+1) × (DSRA Months / 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>• Reference NEXT year's scheduled DS, not current year</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>• Use scheduled DS (straight-line), not actual (includes sweep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>• This avoids circular reference in cash sweep models</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>• Sculpted models: use actual_ds (no circularity — DS derived from CFADS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>• DSRA released at exit (target = 0 in final year)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>═══ QA CHECKS ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>Pass Condition</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>S&amp;U Balance</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>ABS(Total Uses − Total Sources)</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>&lt; $0.01mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Debt Payoff</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>Ending Balance at Debt Tenor</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>&lt; $1mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>MIN(DSCR Y1:Yn)</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>≥ 1.25x (sweep) or 1.30x (sculpt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>No Errors</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Scan for #REF, #NAME, #VALUE, #DIV/0</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>═══ COMMON MISTAKES ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Fuel cost ÷ 1E6</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>Fuel = $30B (should be $30mm)</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>Use ÷ 1E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>DSRA = current DS</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>Circular reference error</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>Reference NEXT column</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>Exit Equity = Exit EV</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>IRR 5-10% too high</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>Subtract debt, add DSRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>Peaker CF × 8760</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>Generation 10× too high</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>Use Dispatch Hours × Avail</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>Hardcoded row numbers</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>Formulas break when rows move</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>Use rows dict: rows['ebitda']</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -800,7 +1234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -931,7 +1365,7 @@
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr"/>
-      <c r="D5" s="12">
+      <c r="D5" s="25">
         <f>MIN(E67:K67)</f>
         <v/>
       </c>
@@ -948,7 +1382,7 @@
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="13">
+      <c r="D6" s="26">
         <f>D98</f>
         <v/>
       </c>
@@ -965,7 +1399,7 @@
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr"/>
-      <c r="D7" s="12">
+      <c r="D7" s="25">
         <f>D99</f>
         <v/>
       </c>
@@ -1072,7 +1506,7 @@
           <t>[INPUT] Legal, advisory</t>
         </is>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="27" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -1092,7 +1526,7 @@
           <t>[INPUT] On exit EBITDA</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="28" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1172,7 +1606,7 @@
           <t>[INPUT] Capacity factor or utilization</t>
         </is>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="27" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1192,7 +1626,7 @@
           <t>[INPUT] All prices/costs</t>
         </is>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="27" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -1312,7 +1746,7 @@
           <t>[INPUT] Debt / EV</t>
         </is>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="27" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1332,7 +1766,7 @@
           <t>[INPUT] All-in rate</t>
         </is>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="27" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -1392,7 +1826,7 @@
           <t>[INPUT] For sweep structure</t>
         </is>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="27" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -1412,7 +1846,7 @@
           <t>[INPUT] Distribution threshold</t>
         </is>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="28" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -1452,7 +1886,7 @@
           <t>[INPUT] Blended rate</t>
         </is>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="27" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1472,7 +1906,7 @@
           <t>[INPUT] % of EV</t>
         </is>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="27" t="n">
         <v>0.85</v>
       </c>
     </row>
@@ -2455,43 +2889,43 @@
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr"/>
-      <c r="E67" s="12">
+      <c r="E67" s="25">
         <f>IF(E62&gt;0,E56/E62,0)</f>
         <v/>
       </c>
-      <c r="F67" s="12">
+      <c r="F67" s="25">
         <f>IF(F62&gt;0,F56/F62,0)</f>
         <v/>
       </c>
-      <c r="G67" s="12">
+      <c r="G67" s="25">
         <f>IF(G62&gt;0,G56/G62,0)</f>
         <v/>
       </c>
-      <c r="H67" s="12">
+      <c r="H67" s="25">
         <f>IF(H62&gt;0,H56/H62,0)</f>
         <v/>
       </c>
-      <c r="I67" s="12">
+      <c r="I67" s="25">
         <f>IF(I62&gt;0,I56/I62,0)</f>
         <v/>
       </c>
-      <c r="J67" s="12">
+      <c r="J67" s="25">
         <f>IF(J62&gt;0,J56/J62,0)</f>
         <v/>
       </c>
-      <c r="K67" s="12">
+      <c r="K67" s="25">
         <f>IF(K62&gt;0,K56/K62,0)</f>
         <v/>
       </c>
-      <c r="L67" s="12">
+      <c r="L67" s="25">
         <f>IF(L62&gt;0,L56/L62,0)</f>
         <v/>
       </c>
-      <c r="M67" s="12">
+      <c r="M67" s="25">
         <f>IF(M62&gt;0,M56/M62,0)</f>
         <v/>
       </c>
-      <c r="N67" s="12">
+      <c r="N67" s="25">
         <f>IF(N62&gt;0,N56/N62,0)</f>
         <v/>
       </c>
@@ -3228,7 +3662,7 @@
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr"/>
-      <c r="D98" s="13">
+      <c r="D98" s="26">
         <f>IRR(D97:K97)</f>
         <v/>
       </c>
@@ -3245,7 +3679,7 @@
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr"/>
-      <c r="D99" s="12">
+      <c r="D99" s="25">
         <f>SUMIF(D97:K97,"&gt;0")/ABS(D97)</f>
         <v/>
       </c>

--- a/deliverables/deliverables-20260120-0030/Master_Template.xlsx
+++ b/deliverables/deliverables-20260120-0030/Master_Template.xlsx
@@ -1366,7 +1366,7 @@
       </c>
       <c r="C5" s="10" t="inlineStr"/>
       <c r="D5" s="25">
-        <f>MIN(E67:K67)</f>
+        <f>IF(COUNTIF(E67:K67,"&gt;0")&gt;0,MINIFS(E67:K67,E67:K67,"&gt;0"),0)</f>
         <v/>
       </c>
     </row>
